--- a/study_case_model/scenario_variables/other_experiment_data/price_scenarios135.xlsx
+++ b/study_case_model/scenario_variables/other_experiment_data/price_scenarios135.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,22 +417,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>stage</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>scenario_index</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>node</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
@@ -463,7 +451,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>29.73191408992884</v>
+        <v>32.37620791745756</v>
       </c>
     </row>
     <row r="3">
@@ -479,7 +467,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>24.31769921945344</v>
+        <v>26.02373911851042</v>
       </c>
     </row>
     <row r="4">
@@ -495,7 +483,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>22.09908741101718</v>
+        <v>28.45949899128703</v>
       </c>
     </row>
     <row r="5">
@@ -511,7 +499,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>31.00965938901951</v>
+        <v>27.65104421285681</v>
       </c>
     </row>
     <row r="6">
@@ -527,7 +515,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>30.18966345718518</v>
+        <v>29.53011656085197</v>
       </c>
     </row>
     <row r="7">
@@ -543,7 +531,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>28.23212301598528</v>
+        <v>30.47552560368331</v>
       </c>
     </row>
     <row r="8">
@@ -559,7 +547,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>29.86712643578832</v>
+        <v>32.70122286277999</v>
       </c>
     </row>
     <row r="9">
@@ -575,7 +563,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>24.64239723464079</v>
+        <v>26.10723100765465</v>
       </c>
     </row>
     <row r="10">
@@ -591,7 +579,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>21.80180413747308</v>
+        <v>28.15500639822899</v>
       </c>
     </row>
     <row r="11">
@@ -607,7 +595,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>31.2785816778712</v>
+        <v>27.24808897339387</v>
       </c>
     </row>
     <row r="12">
@@ -623,7 +611,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>29.72676184612688</v>
+        <v>29.63312435323784</v>
       </c>
     </row>
     <row r="13">
@@ -639,7 +627,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>29.06174143347123</v>
+        <v>30.24069305693786</v>
       </c>
     </row>
     <row r="14">
@@ -655,7 +643,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>30.47236471401422</v>
+        <v>32.43524745580911</v>
       </c>
     </row>
     <row r="15">
@@ -671,7 +659,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>24.33648029200826</v>
+        <v>26.25893551032041</v>
       </c>
     </row>
     <row r="16">
@@ -687,7 +675,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>21.68683176001019</v>
+        <v>28.24985259964706</v>
       </c>
     </row>
     <row r="17">
@@ -703,7 +691,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>31.39863345117894</v>
+        <v>27.27920916535204</v>
       </c>
     </row>
     <row r="18">
@@ -719,7 +707,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>30.35333177557169</v>
+        <v>29.10565972939916</v>
       </c>
     </row>
     <row r="19">
@@ -735,7 +723,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>28.50801226324119</v>
+        <v>30.35903095455533</v>
       </c>
     </row>
     <row r="20">
@@ -751,7 +739,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>29.66241514934023</v>
+        <v>32.78534507387584</v>
       </c>
     </row>
     <row r="21">
@@ -767,7 +755,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>24.35627780396761</v>
+        <v>26.21005302834858</v>
       </c>
     </row>
     <row r="22">
@@ -783,7 +771,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>21.49100601324901</v>
+        <v>28.00115937798844</v>
       </c>
     </row>
     <row r="23">
@@ -799,7 +787,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>30.66451597859409</v>
+        <v>27.49752082945995</v>
       </c>
     </row>
     <row r="24">
@@ -815,7 +803,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>29.58128387668009</v>
+        <v>28.92198771012409</v>
       </c>
     </row>
     <row r="25">
@@ -831,7 +819,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>28.43781842435984</v>
+        <v>29.85897608541561</v>
       </c>
     </row>
     <row r="26">
@@ -847,7 +835,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>29.77724683976426</v>
+        <v>32.47025937575201</v>
       </c>
     </row>
     <row r="27">
@@ -863,7 +851,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>24.4823111796797</v>
+        <v>26.28737044716383</v>
       </c>
     </row>
     <row r="28">
@@ -879,7 +867,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>22.12163865129158</v>
+        <v>28.22114952550069</v>
       </c>
     </row>
     <row r="29">
@@ -895,7 +883,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>30.63984911453933</v>
+        <v>27.83860774070085</v>
       </c>
     </row>
     <row r="30">
@@ -911,7 +899,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>30.17546320725552</v>
+        <v>29.5986533859168</v>
       </c>
     </row>
     <row r="31">
@@ -927,7 +915,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>28.59652811193839</v>
+        <v>30.23679197153542</v>
       </c>
     </row>
     <row r="32">
@@ -943,7 +931,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>29.06773819375302</v>
+        <v>31.38773751939545</v>
       </c>
     </row>
     <row r="33">
@@ -959,7 +947,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>28.27282888903715</v>
+        <v>29.97428287434502</v>
       </c>
     </row>
     <row r="34">
@@ -975,7 +963,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>29.32631527393385</v>
+        <v>31.08561136078287</v>
       </c>
     </row>
     <row r="35">
@@ -991,7 +979,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>26.65662395498384</v>
+        <v>27.97781657534463</v>
       </c>
     </row>
     <row r="36">
@@ -1007,7 +995,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>30.33877797875418</v>
+        <v>32.14927684841976</v>
       </c>
     </row>
     <row r="37">
@@ -1023,7 +1011,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>24.31628542873299</v>
+        <v>24.5848894321725</v>
       </c>
     </row>
     <row r="38">
@@ -1039,7 +1027,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>29.16621967231788</v>
+        <v>31.55674953720092</v>
       </c>
     </row>
     <row r="39">
@@ -1055,7 +1043,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>28.77284691686021</v>
+        <v>30.74190701694813</v>
       </c>
     </row>
     <row r="40">
@@ -1071,7 +1059,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>29.47015758451484</v>
+        <v>31.05755233061704</v>
       </c>
     </row>
     <row r="41">
@@ -1087,7 +1075,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>26.41406812261203</v>
+        <v>28.17152628846243</v>
       </c>
     </row>
     <row r="42">
@@ -1103,7 +1091,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>30.09962327034922</v>
+        <v>32.26702148377129</v>
       </c>
     </row>
     <row r="43">
@@ -1119,7 +1107,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>24.06271687354819</v>
+        <v>24.69049725620035</v>
       </c>
     </row>
     <row r="44">
@@ -1135,7 +1123,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>28.8967575805755</v>
+        <v>31.46405835013729</v>
       </c>
     </row>
     <row r="45">
@@ -1151,7 +1139,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>28.41723247446754</v>
+        <v>30.28163968612322</v>
       </c>
     </row>
     <row r="46">
@@ -1167,7 +1155,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>30.0806185569399</v>
+        <v>31.12173618251279</v>
       </c>
     </row>
     <row r="47">
@@ -1183,7 +1171,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>26.40351265599059</v>
+        <v>27.84191340418993</v>
       </c>
     </row>
     <row r="48">
@@ -1199,7 +1187,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>30.03625545896035</v>
+        <v>32.05371340974747</v>
       </c>
     </row>
     <row r="49">
@@ -1215,7 +1203,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>24.31119539197609</v>
+        <v>24.9134132247394</v>
       </c>
     </row>
     <row r="50">
@@ -1231,7 +1219,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>28.92152510420045</v>
+        <v>31.84927519042535</v>
       </c>
     </row>
     <row r="51">
@@ -1247,7 +1235,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>28.26106544056852</v>
+        <v>30.56827334180117</v>
       </c>
     </row>
     <row r="52">
@@ -1263,7 +1251,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>29.71949240471638</v>
+        <v>31.76082121543738</v>
       </c>
     </row>
     <row r="53">
@@ -1279,7 +1267,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>26.15256777806851</v>
+        <v>27.8435021560558</v>
       </c>
     </row>
     <row r="54">
@@ -1295,7 +1283,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>30.75707631329013</v>
+        <v>32.3254015544051</v>
       </c>
     </row>
     <row r="55">
@@ -1311,7 +1299,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>24.63167716413261</v>
+        <v>24.83541005852825</v>
       </c>
     </row>
     <row r="56">
@@ -1327,7 +1315,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>28.90391132829972</v>
+        <v>32.08116773782046</v>
       </c>
     </row>
     <row r="57">
@@ -1343,7 +1331,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>27.9744377317584</v>
+        <v>30.03309182447316</v>
       </c>
     </row>
     <row r="58">
@@ -1359,7 +1347,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>29.7440925367003</v>
+        <v>30.83028634524889</v>
       </c>
     </row>
     <row r="59">
@@ -1375,7 +1363,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>26.64389001161562</v>
+        <v>27.89062830849778</v>
       </c>
     </row>
     <row r="60">
@@ -1391,7 +1379,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>30.48782460623898</v>
+        <v>31.36523828659454</v>
       </c>
     </row>
     <row r="61">
@@ -1407,7 +1395,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>24.68353810667252</v>
+        <v>24.65962519155677</v>
       </c>
     </row>
     <row r="62">
@@ -1423,7 +1411,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>27.69087584865423</v>
+        <v>29.71279747765334</v>
       </c>
     </row>
     <row r="63">
@@ -1439,7 +1427,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>26.91770554093613</v>
+        <v>27.67716167219539</v>
       </c>
     </row>
     <row r="64">
@@ -1455,7 +1443,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>26.49574936817388</v>
+        <v>26.4684336262495</v>
       </c>
     </row>
     <row r="65">
@@ -1471,7 +1459,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>26.46464153713485</v>
+        <v>30.22303276136843</v>
       </c>
     </row>
     <row r="66">
@@ -1487,7 +1475,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>33.75608230288519</v>
+        <v>27.80713540848814</v>
       </c>
     </row>
     <row r="67">
@@ -1503,7 +1491,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>22.91500500766918</v>
+        <v>33.9632382958333</v>
       </c>
     </row>
     <row r="68">
@@ -1519,7 +1507,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>27.59637576827031</v>
+        <v>29.6710963291215</v>
       </c>
     </row>
     <row r="69">
@@ -1535,7 +1523,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>27.19504138885268</v>
+        <v>27.77154425961481</v>
       </c>
     </row>
     <row r="70">
@@ -1551,7 +1539,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>26.86190948127858</v>
+        <v>26.03002939518295</v>
       </c>
     </row>
     <row r="71">
@@ -1567,7 +1555,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>26.97632360994132</v>
+        <v>30.20976828109887</v>
       </c>
     </row>
     <row r="72">
@@ -1583,7 +1571,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>34.62054443066369</v>
+        <v>27.87021871747368</v>
       </c>
     </row>
     <row r="73">
@@ -1599,7 +1587,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>22.39152748453487</v>
+        <v>34.00003851620959</v>
       </c>
     </row>
     <row r="74">
@@ -1615,7 +1603,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>27.60419063026459</v>
+        <v>29.42716853220322</v>
       </c>
     </row>
     <row r="75">
@@ -1631,7 +1619,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>27.41764398767017</v>
+        <v>28.00975019412886</v>
       </c>
     </row>
     <row r="76">
@@ -1647,7 +1635,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>27.04952087068331</v>
+        <v>26.34807061749592</v>
       </c>
     </row>
     <row r="77">
@@ -1663,7 +1651,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>27.15182687011762</v>
+        <v>30.03365570065553</v>
       </c>
     </row>
     <row r="78">
@@ -1679,7 +1667,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>33.9644449741869</v>
+        <v>27.10614746331163</v>
       </c>
     </row>
     <row r="79">
@@ -1695,7 +1683,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>22.43015116553316</v>
+        <v>33.95556200702102</v>
       </c>
     </row>
     <row r="80">
@@ -1711,7 +1699,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>27.90380835977319</v>
+        <v>29.94165239023408</v>
       </c>
     </row>
     <row r="81">
@@ -1727,7 +1715,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>27.43515721012245</v>
+        <v>27.64858281648149</v>
       </c>
     </row>
     <row r="82">
@@ -1743,7 +1731,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>27.08675509174003</v>
+        <v>26.25956471403307</v>
       </c>
     </row>
     <row r="83">
@@ -1759,7 +1747,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>26.79474059924276</v>
+        <v>29.85121707064548</v>
       </c>
     </row>
     <row r="84">
@@ -1775,7 +1763,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>34.12745528186069</v>
+        <v>27.25125829499971</v>
       </c>
     </row>
     <row r="85">
@@ -1791,7 +1779,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>22.77425202028684</v>
+        <v>34.11167310117945</v>
       </c>
     </row>
     <row r="86">
@@ -1807,7 +1795,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>28.12337130469496</v>
+        <v>29.97609903350135</v>
       </c>
     </row>
     <row r="87">
@@ -1823,7 +1811,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>27.310341058436</v>
+        <v>27.77776770335474</v>
       </c>
     </row>
     <row r="88">
@@ -1839,7 +1827,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>26.82142322827903</v>
+        <v>26.56599605887504</v>
       </c>
     </row>
     <row r="89">
@@ -1855,7 +1843,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>26.69861700023914</v>
+        <v>29.33279840353109</v>
       </c>
     </row>
     <row r="90">
@@ -1871,7 +1859,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>34.17467349743064</v>
+        <v>27.12276101742702</v>
       </c>
     </row>
     <row r="91">
@@ -1887,7 +1875,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>22.3271308749389</v>
+        <v>34.59676874312547</v>
       </c>
     </row>
   </sheetData>
